--- a/data/dividends_info_20260719.xlsx
+++ b/data/dividends_info_20260719.xlsx
@@ -4041,7 +4041,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cyberoo S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Cyberoo S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4238,14 +4238,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4255,14 +4255,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4279,7 +4279,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4289,14 +4289,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4340,14 +4340,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4364,7 +4364,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4381,7 +4381,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4391,14 +4391,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4408,14 +4408,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4432,7 +4432,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4442,14 +4442,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4466,7 +4466,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4517,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4527,14 +4527,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4544,14 +4544,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4561,14 +4561,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4585,7 +4585,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4595,14 +4595,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4612,14 +4612,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4636,7 +4636,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4653,7 +4653,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4663,14 +4663,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4680,14 +4680,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4697,14 +4697,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4714,14 +4714,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4738,7 +4738,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4748,14 +4748,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4765,14 +4765,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4782,14 +4782,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4806,7 +4806,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4823,7 +4823,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4833,14 +4833,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4850,14 +4850,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4874,7 +4874,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4884,14 +4884,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4901,14 +4901,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4918,14 +4918,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4942,7 +4942,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4952,14 +4952,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4969,14 +4969,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4993,7 +4993,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5003,14 +5003,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5020,14 +5020,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5037,14 +5037,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5061,7 +5061,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5071,14 +5071,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5088,14 +5088,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5105,14 +5105,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5122,14 +5122,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5139,14 +5139,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5156,14 +5156,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5180,7 +5180,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5190,14 +5190,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5207,14 +5207,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5231,7 +5231,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5248,7 +5248,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5265,7 +5265,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5282,7 +5282,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5367,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5377,14 +5377,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5394,14 +5394,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5418,7 +5418,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5445,14 +5445,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5469,7 +5469,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5496,14 +5496,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5520,7 +5520,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5530,14 +5530,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5554,7 +5554,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5564,14 +5564,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5581,14 +5581,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5598,14 +5598,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5615,14 +5615,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5639,7 +5639,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5656,7 +5656,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5683,14 +5683,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5700,14 +5700,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5724,7 +5724,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5734,14 +5734,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5751,14 +5751,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5775,7 +5775,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5802,14 +5802,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5826,7 +5826,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5843,7 +5843,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5853,14 +5853,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5877,7 +5877,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5887,14 +5887,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5911,7 +5911,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5928,7 +5928,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5945,7 +5945,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5955,14 +5955,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5972,14 +5972,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6013,7 +6013,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6030,7 +6030,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6047,7 +6047,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -6074,14 +6074,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6098,7 +6098,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6108,14 +6108,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6125,14 +6125,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6149,7 +6149,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6166,7 +6166,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6183,7 +6183,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6193,14 +6193,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -6227,14 +6227,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6251,7 +6251,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6261,14 +6261,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6285,7 +6285,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6295,14 +6295,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6319,7 +6319,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6329,14 +6329,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6346,14 +6346,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6363,14 +6363,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6387,7 +6387,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6404,7 +6404,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6414,14 +6414,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6431,14 +6431,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6448,14 +6448,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6472,7 +6472,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6482,14 +6482,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6499,14 +6499,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6516,14 +6516,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6540,7 +6540,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6557,7 +6557,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6567,14 +6567,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6584,14 +6584,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
